--- a/etl/data/inputs/Dr Verweys Tank Cleaning Guide Oil - procedure templates.xlsx
+++ b/etl/data/inputs/Dr Verweys Tank Cleaning Guide Oil - procedure templates.xlsx
@@ -13,14 +13,14 @@
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -97,19 +97,19 @@
     <t xml:space="preserve">J</t>
   </si>
   <si>
-    <t xml:space="preserve">Cleaning Code I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source cleaning code I. Use the cleaning-method matrix below to determine its required operations.</t>
+    <t xml:space="preserve">Cleaning Code J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source cleaning code J. Use the cleaning-method matrix below to determine its required operations.</t>
   </si>
   <si>
     <t xml:space="preserve">JJ</t>
   </si>
   <si>
-    <t xml:space="preserve">Cleaning Code II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source cleaning code II. Use the cleaning-method matrix below to determine its required operations.</t>
+    <t xml:space="preserve">Cleaning Code JJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source cleaning code JJ. Use the cleaning-method matrix below to determine its required operations.</t>
   </si>
   <si>
     <t xml:space="preserve">OO(e)</t>
@@ -137,6 +137,15 @@
   </si>
   <si>
     <t xml:space="preserve">Source cleaning code OO. Use the cleaning-method matrix below to determine its required operations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleaning Code U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source cleaning code U. Use the cleaning-method matrix below to determine its required operations.</t>
   </si>
 </sst>
 </file>
@@ -146,7 +155,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -181,6 +190,21 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -233,8 +257,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -244,6 +272,14 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -323,216 +359,233 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="101.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="113.93"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
